--- a/products.xlsx
+++ b/products.xlsx
@@ -453,7 +453,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:R4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>

--- a/products.xlsx
+++ b/products.xlsx
@@ -452,8 +452,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -570,139 +570,351 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Tech &amp; Electronics</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>UGREEN 2 Pack 100W USB C to USB C Cable 1M, PD Fast Charging Type C Cord | USB2.0 480Mbps Data Transfer Compatible with iPhone 17/16, Galaxy S26, MacBook Air/Pro, iPad Pro/Air, Dell XPS, Pixel</t>
+          <t>Versuni Philips Lint Shaver, Lint Remover for Clothes, Suitable for All Textiles, 2 Height Settings, Battery Operated (2 x AA Batteries Included), Black (GC026/80)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>https://link.amazon/B0afrj4vA</t>
+          <t>https://www.amazon.com.au/Removing-Batteries-Adjustment-GC026-80/dp/B07M8J529S?pd_rd_w=aCcnA&amp;content-id=amzn1.sym.b92b7e1a-6391-4709-aba6-d845e97783a1&amp;pf_rd_p=b92b7e1a-6391-4709-aba6-d845e97783a1&amp;pf_rd_r=WMGGZPQG5KCP9W7MY05A&amp;pd_rd_wg=Kh9la&amp;pd_rd_r=a0781eb1-c454-4389-8ce3-0e25b81370ac&amp;pd_rd_i=B07M8J529S&amp;th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=86868a853d30dc10a1c891703eabe845&amp;ref_=as_li_ss_tl</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="n"/>
-      <c r="H2" s="2" t="n"/>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
+      <c r="F2" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1258</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>5K+ bought in past month</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>30 Jul</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>FREE delivery for Prime members</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Home &amp; Office</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Squishy Cube Stress Ball with Ocean Seashell Fillers, Slow Rise for Adults | Soft Gel Texture | Slow-Rising Squeeze | Ocean-Inspired Fillers | Desk Fidget for Office and Home | Reusable Sensory Toy</t>
+          <t>Trading in the Zone — Mark Douglas</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>https://link.amazon/B09GWo8WV</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+          <t>https://link.amazon/B0frVzefy</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>The classic on trading psychology — why discipline beats prediction.</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>4.7</v>
+      </c>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>31 Jul</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
       <c r="R3" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Versuni Philips Lint Shaver, Lint Remover for Clothes, Suitable for All Textiles, 2 Height Settings, Battery Operated (2 x AA Batteries Included), Black (GC026/80)</t>
+          <t>How to Day Trade for a Living — Andrew Aziz</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>https://www.amazon.com.au/Removing-Batteries-Adjustment-GC026-80/dp/B07M8J529S?pd_rd_w=aCcnA&amp;content-id=amzn1.sym.b92b7e1a-6391-4709-aba6-d845e97783a1&amp;pf_rd_p=b92b7e1a-6391-4709-aba6-d845e97783a1&amp;pf_rd_r=WMGGZPQG5KCP9W7MY05A&amp;pd_rd_wg=Kh9la&amp;pd_rd_r=a0781eb1-c454-4389-8ce3-0e25b81370ac&amp;pd_rd_i=B07M8J529S&amp;th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=86868a853d30dc10a1c891703eabe845&amp;ref_=as_li_ss_tl</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
+          <t>https://link.amazon/B00Vd0Dsk</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Amazon's long-running #1 beginner trading book: tools, tactics, money management.</t>
+        </is>
+      </c>
       <c r="F4" s="2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>1258</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5K+ bought in past month</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>19.95</v>
-      </c>
+        <v>4.6</v>
+      </c>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30 Jul</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>FREE delivery for Prime members</t>
-        </is>
-      </c>
+          <t>31 Jul</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="n"/>
       <c r="Q4" s="2" t="n"/>
       <c r="R4" s="2" t="n">
-        <v>20</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>p6</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Best Loser Wins — Tom Hougaard</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B024b51aZ</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>A high-stakes trader on why handling losses well is the real edge.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>31 Jul</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
+      <c r="P5" s="2" t="n"/>
+      <c r="Q5" s="2" t="n"/>
+      <c r="R5" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>p7</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Technical Analysis of the Financial Markets — John J. Murphy</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B0awNruH8</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>The reference bible for charts, trends and indicators.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>31 Jul</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>p8</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Japanese Candlestick Charting Techniques — Steve Nison</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B09dNW1dw</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>The book that brought candlesticks to the West.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>31 Jul</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="n"/>
+      <c r="Q7" s="2" t="n"/>
+      <c r="R7" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>p9</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Market Wizards — Jack D. Schwager</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://link.amazon/B034hwFXs</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Interviews with the world's top traders — how the best actually think.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>31 Jul</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kim_p\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE34E354-2F03-4EA2-8D2B-9833FCC87191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{690A3E3A-C269-4CB4-BF16-6D8AACF27F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="321">
   <si>
     <t>id</t>
   </si>
@@ -173,60 +173,27 @@
     <t>App + remote + speaker</t>
   </si>
   <si>
-    <t>Everfit 420mm Foldable Walking Pad</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B0BW2HT211?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Wide belt, up to 12km/h</t>
-  </si>
-  <si>
     <t>Smart Scales</t>
   </si>
   <si>
     <t>eufy Smart Scale P2</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B09NJJ752J?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Wi-Fi + Bluetooth, 15 measurements</t>
   </si>
   <si>
     <t>eufy Smart Scale P2 Pro</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B09PDTB2XB?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>16 measurements incl. heart rate</t>
   </si>
   <si>
-    <t>RENPHO Elis 1 Body Fat Scale</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B01N1UX8RW?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>RENPHO Elis 1 USB-C Rechargeable Scale</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B079DQ7JK6?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Rechargeable version</t>
-  </si>
-  <si>
     <t>Meal Prep</t>
   </si>
   <si>
     <t>Sistema Multi Split To Go (5 Pack)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B08HB4GLKK?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>NZ brand Aussies know, divided containers</t>
   </si>
   <si>
@@ -236,69 +203,24 @@
     <t>TriggerPoint GRID Foam Roller 33cm</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B08WR2NPLH?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Physio-trusted classic</t>
   </si>
   <si>
     <t>Supplements</t>
   </si>
   <si>
-    <t>Optimum Nutrition Gold Standard 100% Whey 907g (Double Rich Chocolate)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B07B2X7H1F?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>World's best-selling whey, 24g protein/serve</t>
-  </si>
-  <si>
-    <t>Optimum Nutrition Micronized Creatine 300g</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B07774XR8W?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Amazon's Choice, 3K+ bought/month, #2 in category</t>
-  </si>
-  <si>
-    <t>Optimum Nutrition Micronised Creatine 1.2kg (Bulk)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B002DYIZEY?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Bulk size for regulars</t>
-  </si>
-  <si>
-    <t>Optimum Nutrition Flavoured Creatine 360g (Blueberry Lemonade)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B0DGH2BWRD?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Flavoured option, 60 serves</t>
-  </si>
-  <si>
     <t>Shakers</t>
   </si>
   <si>
     <t>BlenderBottle Classic 28oz</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B00MVMCUK8?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>The original shaker, BlenderBall whisk</t>
   </si>
   <si>
     <t>BlenderBottle Sport Insulated Stainless Steel 24oz</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B084PVQGH1?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Premium insulated, keeps drinks cold 24hrs</t>
   </si>
   <si>
@@ -308,27 +230,18 @@
     <t>Gaiam Folding Travel Yoga Mat 2mm</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B019DKV5MY?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Folds to fit a gym bag</t>
   </si>
   <si>
     <t>Amazon Basics High-Density Foam Roller 30cm</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B018KFP8E4?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Budget roller, top-2 in every roundup</t>
   </si>
   <si>
     <t>PROIRON Resistance Bands Set 14-Piece (Tubes + Handles + Door Anchor)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B07V6WDSFV?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Full home-gym-in-a-bag, sold by PROIRON AU</t>
   </si>
   <si>
@@ -338,18 +251,12 @@
     <t>TriggerPoint MobiPoint Massage Ball</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B01LX72D9A?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>4.6/3,930 — feet, hands, forearms</t>
   </si>
   <si>
     <t>Etekcity Smart Body Scale ESF-551</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B095YJW56C?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>US #1 scale brand, sold by VESYNC AU</t>
   </si>
   <si>
@@ -359,54 +266,36 @@
     <t>Everfit 18kg Adjustable Kettlebell</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0CZMZH4M5?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Aussie brand, adjustable 4.5-18kg</t>
   </si>
   <si>
     <t>Everfit 20kg Kettlebell (Neoprene Coated)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0CZN1RBLN?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Heavy single bell</t>
   </si>
   <si>
     <t>PROIRON Neoprene Kettlebell (4-20kg options)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B09TNDJFY9?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Colour-coded, cast iron core</t>
   </si>
   <si>
     <t>PROIRON Soft PVC Kettlebell (2-10kg)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B09PYR47LY?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Floor-safe soft base, beginner pick</t>
   </si>
   <si>
     <t>PROIRON Cast Iron Kettlebell (4-24kg)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0887VXHGW?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Pro flat-bottom cast iron</t>
   </si>
   <si>
     <t>PROIRON Neoprene Dumbbells Pair (1-10kg)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B088BF7F4F?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Brand line rated 4.8 with 21K+ reviews</t>
   </si>
   <si>
@@ -416,27 +305,18 @@
     <t>PROIRON Ab Roller Wheel with Knee Pad</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0BX5Y5HLN?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>4.4/621, $24.74 impulse-buy zone</t>
   </si>
   <si>
     <t>PROIRON Foldable 4-Wheel Ab Roller</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B08NDSYK2L?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Extra-stable 4-wheel design</t>
   </si>
   <si>
     <t>PROIRON Spring-Rebound Ab Roller</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0C287R83G?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Auto-rebound assist for beginners</t>
   </si>
   <si>
@@ -1044,6 +924,66 @@
   </si>
   <si>
     <t>https://www.amazon.com.au/dp/B0CJ8WZZ4X?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=693a8937aff2e0af3dc0a3d04e7de561&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B09NJJ752J?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=ce56150c47f7a0d4450a58ca3631177c&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B09PDTB2XB?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=b9fbc8467e99f15502629b4d4ad9cdb3&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B08HB4GLKK?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=1dd9ce5d976faa45ba8cd790fb424f65&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B08MKVJC1F?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=d63a8cd814bd49f56a1e52b0e2b77d33&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B00MVMCUK8?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=1f618d0d77b69fa4a8a6d116e4cc4f7f&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B084PVQGH1?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=b3d06840105c1889fd2c7743bb59c271&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B073WRCQQK?th=1&amp;psc=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=a54db469fb44033e87679d654e13d453&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B00XM2N06O?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=ad66363b6e049bdde12adc20b186b95a&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B07V6WDSFV?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=d915621ce5c012335789962a20d4edea&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B01LX72D9A?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=36247207e31c66b9aac82764dcfb27e3&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B095YJW56C?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=84b311aa7f7c6483b81bc3f37006134c&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B0CZMZH4M5?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=45c3b8ffa74b75b35cdc1db9e36615a8&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B0CZN1RBLN?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=d1e4023d9ecead1693053bc7df68eae1&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B09T9K62HZ?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=492a15466eb21b2056aa25a8995a9c32&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B09BDR4LCQ?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=1722c285ebdbb35930fd40d03038d9d4&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B01C9PWJKC?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=c02e75baa65bb79290cb46ae748872c5&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B01N5WDPR3?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=b32f335cb78140df9bd79d056935c7a1&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B0BX5Y5HLN?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=a7a96e3ae4e9488381fa375beac5ea76&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B07SZCJJ9Q?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=561393a7430f8ead21fd3d21d5417354&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B0BVFBYN1X?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=f3a94ea2788fb908053a23cd5962fa65&amp;ref_=as_li_ss_tl</t>
   </si>
 </sst>
 </file>
@@ -1426,7 +1366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S98"/>
+  <dimension ref="A1:S91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1460,7 +1400,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>327</v>
+        <v>287</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -1516,7 +1456,7 @@
         <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>328</v>
+        <v>288</v>
       </c>
       <c r="E2" s="6">
         <v>0.1</v>
@@ -1557,7 +1497,7 @@
         <v>22</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>329</v>
+        <v>289</v>
       </c>
       <c r="E3" s="6">
         <v>0.1</v>
@@ -1596,7 +1536,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="E4" s="6">
         <v>0.1</v>
@@ -1631,7 +1571,7 @@
         <v>26</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>331</v>
+        <v>291</v>
       </c>
       <c r="E5" s="6">
         <v>0.1</v>
@@ -1668,7 +1608,7 @@
         <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="E6" s="6">
         <v>0.1</v>
@@ -1709,7 +1649,7 @@
         <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>333</v>
+        <v>293</v>
       </c>
       <c r="E7" s="6">
         <v>0.1</v>
@@ -1750,7 +1690,7 @@
         <v>33</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>334</v>
+        <v>294</v>
       </c>
       <c r="E8" s="6">
         <v>0.05</v>
@@ -1791,7 +1731,7 @@
         <v>35</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>335</v>
+        <v>295</v>
       </c>
       <c r="E9" s="6">
         <v>0.05</v>
@@ -1834,7 +1774,7 @@
         <v>37</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>336</v>
+        <v>296</v>
       </c>
       <c r="E10" s="6">
         <v>0.05</v>
@@ -1877,7 +1817,7 @@
         <v>40</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>337</v>
+        <v>297</v>
       </c>
       <c r="E11" s="6">
         <v>0.05</v>
@@ -1918,7 +1858,7 @@
         <v>43</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>338</v>
+        <v>298</v>
       </c>
       <c r="E12" s="6">
         <v>0.05</v>
@@ -1953,7 +1893,7 @@
         <v>46</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>339</v>
+        <v>299</v>
       </c>
       <c r="E13" s="6">
         <v>0.05</v>
@@ -1988,7 +1928,7 @@
         <v>48</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>340</v>
+        <v>300</v>
       </c>
       <c r="E14" s="6">
         <v>0.05</v>
@@ -2017,15 +1957,17 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15" s="6"/>
+        <v>301</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.1</v>
+      </c>
       <c r="F15" s="2" t="s">
         <v>52</v>
       </c>
@@ -2050,17 +1992,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="6"/>
-      <c r="F16" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -2083,20 +2027,26 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="G17" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1579</v>
+      </c>
       <c r="I17" s="2"/>
       <c r="J17" s="3" t="s">
         <v>21</v>
@@ -2116,17 +2066,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E18" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -2149,15 +2101,17 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="6"/>
+        <v>305</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.1</v>
+      </c>
       <c r="F19" s="2" t="s">
         <v>64</v>
       </c>
@@ -2182,24 +2136,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G20" s="2">
-        <v>4.5</v>
-      </c>
-      <c r="H20" s="2">
-        <v>1579</v>
-      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="3" t="s">
         <v>21</v>
@@ -2219,17 +2171,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" s="6"/>
-      <c r="F21" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -2252,17 +2206,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" s="6"/>
+        <v>308</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F22" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -2285,34 +2241,28 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G23" s="2">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="H23" s="2">
-        <v>757</v>
-      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
       <c r="I23" s="2"/>
       <c r="J23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K23" s="3">
-        <v>25</v>
-      </c>
-      <c r="L23" s="3">
-        <v>34.950000000000003</v>
-      </c>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -2326,17 +2276,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" s="6"/>
+        <v>310</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F24" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -2359,24 +2311,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" s="6"/>
+        <v>311</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F25" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G25" s="2">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="H25" s="2">
-        <v>2371</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
       <c r="I25" s="2"/>
       <c r="J25" s="3" t="s">
         <v>21</v>
@@ -2396,17 +2346,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E26" s="6"/>
+        <v>312</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F26" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -2429,17 +2381,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E27" s="6"/>
+        <v>313</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F27" s="2" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -2462,17 +2416,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E28" s="6"/>
+        <v>314</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F28" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
@@ -2495,17 +2451,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E29" s="6"/>
+        <v>315</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F29" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -2528,17 +2486,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E30" s="6"/>
+        <v>316</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F30" s="2" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -2561,17 +2521,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E31" s="6"/>
+        <v>317</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F31" s="2" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -2594,17 +2556,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E32" s="6"/>
+        <v>318</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F32" s="2" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -2627,17 +2591,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" s="6"/>
+        <v>319</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F33" s="2" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -2660,17 +2626,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E34" s="6"/>
+        <v>320</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F34" s="2" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -2693,17 +2661,17 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="2" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -2726,17 +2694,17 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -2759,17 +2727,17 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="2" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -2792,17 +2760,17 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="2" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
@@ -2825,17 +2793,17 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="2" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -2858,17 +2826,17 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="E40" s="6"/>
       <c r="F40" s="2" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
@@ -2891,17 +2859,17 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="E41" s="6"/>
       <c r="F41" s="2" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -2924,17 +2892,17 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="E42" s="6"/>
       <c r="F42" s="2" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
@@ -2957,17 +2925,17 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="E43" s="6"/>
       <c r="F43" s="2" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -2990,17 +2958,17 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="E44" s="6"/>
       <c r="F44" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -3023,17 +2991,17 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="E45" s="6"/>
       <c r="F45" s="2" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -3056,17 +3024,17 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="E46" s="6"/>
       <c r="F46" s="2" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -3089,17 +3057,17 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="E47" s="6"/>
       <c r="F47" s="2" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -3122,17 +3090,17 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>73</v>
+        <v>139</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="E48" s="6"/>
       <c r="F48" s="2" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -3155,17 +3123,17 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="E49" s="6"/>
       <c r="F49" s="2" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -3188,17 +3156,17 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="2" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -3221,17 +3189,17 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>39</v>
+        <v>139</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="E51" s="6"/>
       <c r="F51" s="2" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -3254,17 +3222,17 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="E52" s="6"/>
       <c r="F52" s="2" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
@@ -3287,17 +3255,17 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="E53" s="6"/>
       <c r="F53" s="2" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -3320,17 +3288,17 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="E54" s="6"/>
       <c r="F54" s="2" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -3353,17 +3321,17 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="E55" s="6"/>
       <c r="F55" s="2" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
@@ -3386,17 +3354,17 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="E56" s="6"/>
       <c r="F56" s="2" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
@@ -3419,17 +3387,17 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>179</v>
+        <v>79</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="E57" s="6"/>
       <c r="F57" s="2" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -3452,17 +3420,17 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
       <c r="E58" s="6"/>
       <c r="F58" s="2" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -3485,17 +3453,17 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="E59" s="6"/>
       <c r="F59" s="2" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
@@ -3518,17 +3486,17 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>195</v>
+        <v>139</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="E60" s="6"/>
       <c r="F60" s="2" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -3551,17 +3519,17 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>199</v>
+        <v>180</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>200</v>
+        <v>181</v>
       </c>
       <c r="E61" s="6"/>
       <c r="F61" s="2" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
@@ -3584,17 +3552,17 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>169</v>
+        <v>55</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" s="2" t="s">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
@@ -3617,17 +3585,17 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="E63" s="6"/>
       <c r="F63" s="2" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
@@ -3650,17 +3618,17 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>208</v>
+        <v>189</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="2" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
@@ -3683,17 +3651,17 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>211</v>
+        <v>192</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>212</v>
+        <v>193</v>
       </c>
       <c r="E65" s="6"/>
       <c r="F65" s="2" t="s">
-        <v>213</v>
+        <v>194</v>
       </c>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
@@ -3716,17 +3684,17 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="E66" s="6"/>
       <c r="F66" s="2" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
@@ -3749,17 +3717,17 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="E67" s="6"/>
       <c r="F67" s="2" t="s">
-        <v>219</v>
+        <v>200</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -3782,17 +3750,17 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="E68" s="6"/>
       <c r="F68" s="2" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
@@ -3815,17 +3783,17 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>223</v>
+        <v>204</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="E69" s="6"/>
       <c r="F69" s="2" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -3848,17 +3816,17 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>65</v>
+        <v>207</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>227</v>
+        <v>209</v>
       </c>
       <c r="E70" s="6"/>
       <c r="F70" s="2" t="s">
-        <v>228</v>
+        <v>210</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -3881,17 +3849,17 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>73</v>
+        <v>207</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="E71" s="6"/>
       <c r="F71" s="2" t="s">
-        <v>231</v>
+        <v>213</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -3914,17 +3882,17 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>232</v>
+        <v>214</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>233</v>
+        <v>215</v>
       </c>
       <c r="E72" s="6"/>
       <c r="F72" s="2" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -3947,17 +3915,17 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>169</v>
+        <v>207</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>235</v>
+        <v>217</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="E73" s="6"/>
       <c r="F73" s="2" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
@@ -3980,17 +3948,17 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>169</v>
+        <v>61</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="E74" s="6"/>
       <c r="F74" s="2" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
@@ -4013,17 +3981,17 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>169</v>
+        <v>61</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="E75" s="6"/>
       <c r="F75" s="2" t="s">
-        <v>243</v>
+        <v>225</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
@@ -4046,17 +4014,17 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>169</v>
+        <v>61</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="E76" s="6"/>
       <c r="F76" s="2" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -4079,17 +4047,17 @@
         <v>76</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>247</v>
+        <v>61</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="E77" s="6"/>
       <c r="F77" s="2" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
@@ -4112,17 +4080,17 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>247</v>
+        <v>61</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="E78" s="6"/>
       <c r="F78" s="2" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
@@ -4145,17 +4113,17 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>247</v>
+        <v>129</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="E79" s="6"/>
       <c r="F79" s="2" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
@@ -4178,17 +4146,17 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>247</v>
+        <v>129</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="E80" s="6"/>
       <c r="F80" s="2" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
@@ -4211,17 +4179,17 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="E81" s="6"/>
       <c r="F81" s="2" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
@@ -4244,17 +4212,17 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="E82" s="6"/>
       <c r="F82" s="2" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
@@ -4277,17 +4245,17 @@
         <v>82</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="E83" s="6"/>
       <c r="F83" s="2" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -4310,17 +4278,17 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="E84" s="6"/>
       <c r="F84" s="2" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -4343,17 +4311,17 @@
         <v>84</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="E85" s="6"/>
       <c r="F85" s="2" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
@@ -4376,17 +4344,17 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>169</v>
+        <v>61</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="E86" s="6"/>
       <c r="F86" s="2" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -4409,17 +4377,17 @@
         <v>86</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>169</v>
+        <v>61</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="E87" s="6"/>
       <c r="F87" s="2" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
@@ -4442,17 +4410,17 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>169</v>
+        <v>61</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="E88" s="6"/>
       <c r="F88" s="2" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -4475,17 +4443,17 @@
         <v>88</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>169</v>
+        <v>61</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="E89" s="6"/>
       <c r="F89" s="2" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -4508,17 +4476,17 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>169</v>
+        <v>61</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="E90" s="6"/>
       <c r="F90" s="2" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -4541,17 +4509,17 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>110</v>
+        <v>207</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="E91" s="6"/>
       <c r="F91" s="2" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -4568,237 +4536,6 @@
       <c r="Q91" s="2"/>
       <c r="R91" s="2"/>
       <c r="S91" s="2"/>
-    </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="E92" s="6"/>
-      <c r="F92" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K92" s="3"/>
-      <c r="L92" s="3"/>
-      <c r="M92" s="3"/>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
-      <c r="P92" s="2"/>
-      <c r="Q92" s="2"/>
-      <c r="R92" s="2"/>
-      <c r="S92" s="2"/>
-    </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A93" s="2">
-        <v>92</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E93" s="6"/>
-      <c r="F93" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K93" s="3"/>
-      <c r="L93" s="3"/>
-      <c r="M93" s="3"/>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
-      <c r="P93" s="2"/>
-      <c r="Q93" s="2"/>
-      <c r="R93" s="2"/>
-      <c r="S93" s="2"/>
-    </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A94" s="2">
-        <v>93</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E94" s="6"/>
-      <c r="F94" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K94" s="3"/>
-      <c r="L94" s="3"/>
-      <c r="M94" s="3"/>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
-      <c r="P94" s="2"/>
-      <c r="Q94" s="2"/>
-      <c r="R94" s="2"/>
-      <c r="S94" s="2"/>
-    </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A95" s="2">
-        <v>94</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E95" s="6"/>
-      <c r="F95" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K95" s="3"/>
-      <c r="L95" s="3"/>
-      <c r="M95" s="3"/>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
-      <c r="P95" s="2"/>
-      <c r="Q95" s="2"/>
-      <c r="R95" s="2"/>
-      <c r="S95" s="2"/>
-    </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
-        <v>95</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E96" s="6"/>
-      <c r="F96" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-      <c r="J96" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K96" s="3"/>
-      <c r="L96" s="3"/>
-      <c r="M96" s="3"/>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
-      <c r="P96" s="2"/>
-      <c r="Q96" s="2"/>
-      <c r="R96" s="2"/>
-      <c r="S96" s="2"/>
-    </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A97" s="2">
-        <v>96</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E97" s="6"/>
-      <c r="F97" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
-      <c r="J97" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K97" s="3"/>
-      <c r="L97" s="3"/>
-      <c r="M97" s="3"/>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
-      <c r="P97" s="2"/>
-      <c r="Q97" s="2"/>
-      <c r="R97" s="2"/>
-      <c r="S97" s="2"/>
-    </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A98" s="2">
-        <v>97</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E98" s="6"/>
-      <c r="F98" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
-      <c r="J98" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K98" s="3"/>
-      <c r="L98" s="3"/>
-      <c r="M98" s="3"/>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
-      <c r="P98" s="2"/>
-      <c r="Q98" s="2"/>
-      <c r="R98" s="2"/>
-      <c r="S98" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4815,7 +4552,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>314</v>
+        <v>274</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -4823,17 +4560,17 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>315</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>316</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>317</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -4841,37 +4578,37 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>318</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>319</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>320</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>321</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>322</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>323</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>324</v>
+        <v>284</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -4879,12 +4616,12 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>325</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>326</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kim_p\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{690A3E3A-C269-4CB4-BF16-6D8AACF27F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9F6AE3-C4D6-4BEF-827A-6BF467D70205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="294">
   <si>
     <t>id</t>
   </si>
@@ -320,93 +320,21 @@
     <t>Auto-rebound assist for beginners</t>
   </si>
   <si>
-    <t>Musashi High Protein Powder 2kg (Vanilla)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B07QN1VT8V?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Aussie brand, sold by Amazon AU, digestive enzymes</t>
-  </si>
-  <si>
-    <t>Musashi 100% Whey Protein 2kg (Chocolate)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B07QMY4B3S?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>WPC+WPI blend, batch tested</t>
-  </si>
-  <si>
-    <t>Musashi 100% Whey Protein 2kg (Vanilla)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B07QP39QNQ?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Low carb, Informed Sport tested</t>
-  </si>
-  <si>
-    <t>Musashi Bulk Protein 2kg (Vanilla)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B07QMYTVGW?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Mass gainer formula</t>
-  </si>
-  <si>
-    <t>Musashi Bulk Protein 2kg (Chocolate)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B07QMYGY3Y?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Mass gainer, chocolate milkshake</t>
-  </si>
-  <si>
-    <t>Musashi Plant Protein 900g (Vanilla)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B07R69WWY4?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Vegan pea/rice/chia blend</t>
-  </si>
-  <si>
-    <t>Musashi Creatine Monohydrate 350g</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B00HU3IFVQ?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>70 serves, Sport-Informed certified</t>
-  </si>
-  <si>
     <t>Meteor Essential Power Bands (Set of 5)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B08D9CXNTQ?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>208cm pull-up assist loops, Aussie brand</t>
   </si>
   <si>
     <t>Meteor All-in-One Resistance Band Set (5-70kg)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B096KGLC9R?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Bands + handles + ankle straps + door anchor</t>
   </si>
   <si>
     <t>Meteor 200cm Flat Resistance Bands (3 Levels)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B099WL27BS?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Physio-style open-ended bands</t>
   </si>
   <si>
@@ -416,27 +344,18 @@
     <t>PROIRON Push Up Bar Stands (Pair)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B07RWLWV63?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Steel H-frame, 300kg load</t>
   </si>
   <si>
     <t>PROIRON Pull Up Assist Bands</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B083S91LBD?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Heavy duty, colour-coded resistance</t>
   </si>
   <si>
     <t>PROIRON Doorway Pull Up Bar (72-97cm)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0C88TR3DS?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>No screws, 200kg rated, glowing AU reviews</t>
   </si>
   <si>
@@ -446,45 +365,30 @@
     <t>PROIRON Weighted Jump Rope 1LB (Alloy Handles)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0C2BH6GVH?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Weighted handles, praised AU reviews</t>
   </si>
   <si>
     <t>PROIRON NBR Yoga Mat 10mm Thick</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B088FHNXB1?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Extra thick with alignment lines + strap</t>
   </si>
   <si>
     <t>Everfit Magnetic Spin Bike (Wireless Pulse)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0CQ6Y4MJ8?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Quiet magnetic resistance, in stock FBA</t>
   </si>
   <si>
     <t>Everfit Foldable X-Bike Cross Trainer</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0841ZQMZ7?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>8-level resistance, folds away</t>
   </si>
   <si>
     <t>Everfit Spin Bike 13kg Flywheel</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B07R3JF3Y3?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>150kg capacity, LCD + phone holder</t>
   </si>
   <si>
@@ -494,144 +398,84 @@
     <t>Atercel Workout Gloves</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B07RMH8ZJV?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Breathable snug fit, huge global seller</t>
   </si>
   <si>
     <t>Atercel Full Palm Protection Gloves</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B08H86NRXP?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Upgraded high-density padding</t>
   </si>
   <si>
-    <t>TheFitLife Pull Up Assist Bands</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B0D3H9PRNR?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Sold by TheFitLifeAU, FBA</t>
-  </si>
-  <si>
     <t>PROIRON 20kg Walnut-Steel Adjustable Dumbbell Set</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B01N1RDG88?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Premium wood-look plates, pair</t>
   </si>
   <si>
     <t>PROIRON 15kg Cast Iron Adjustable Dumbbell Set</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0CC2DYSMH?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Converts dumbbell to barbell</t>
   </si>
   <si>
     <t>Everfit Magnetic Rowing Machine (Foldable)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B08Z3CZW67?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>8 levels, quiet, 150kg capacity</t>
   </si>
   <si>
     <t>Everfit 16-Level Bluetooth Rowing Machine</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0GKNRLRD8?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>App-compatible, in stock FBA</t>
   </si>
   <si>
     <t>Everfit Elastic Rope Rowing Machine</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B08R8553NB?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Budget rower, folds for storage</t>
   </si>
   <si>
     <t>Everfit Flat Weight Bench (300kg)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B07K5M94LN?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Heavy-duty steel, PU leather</t>
   </si>
   <si>
     <t>Sistema Microwave Rice Cooker 2.6L</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B00BTIVNT4?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Meal-prep hero, cult AU following</t>
   </si>
   <si>
     <t>Sistema Rice Cooker + Container Combo</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B08H9MR8K7?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>4.6 stars / 28,741 reviews, ships from Amazon AU</t>
   </si>
   <si>
-    <t>Optimum Nutrition Creatine Capsules (200ct)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B002DYIZGC?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>2500mg caps, no-mix option</t>
-  </si>
-  <si>
     <t>Armortech Commercial Rubber Gym Flooring 1x1m 15mm</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B07TP9S2JV?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Aussie brand, commercial grade, garage-gym staple</t>
   </si>
   <si>
     <t>Armortech Wall Mount Pull Up Bar PU22</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B07TRT7HLL?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>All-steel commercial duty</t>
   </si>
   <si>
     <t>Armortech Adjustable Weighted Vest 10-30kg</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B07TPB13T3?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Cast iron weights included</t>
   </si>
   <si>
     <t>Everfit 10-in-1 Multi Station Weight Bench (330kg)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0CPDKG7NW?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>AU best-seller in Home Gym Systems</t>
   </si>
   <si>
@@ -984,6 +828,81 @@
   </si>
   <si>
     <t>https://www.amazon.com.au/dp/B0BVFBYN1X?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=f3a94ea2788fb908053a23cd5962fa65&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B08B18HYH6?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=57cf966fbd4f4b6fcfd32c7188ab6ab8&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B096KDV7GM?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=ad810f6542ce5517e498ba66e8f4878c&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B099WLYBLC?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=59dc671c990d5b9f8b274342153e5bf4&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B07RWLWV63?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=79f32a973742181fe5109c790ab7a836&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B07DG1MMM9?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=2f76433c96ef7f16722df67f37a10e87&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B0C88MN138?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=53f835009eb53373243943ed6b089fb6&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B0BR4Z75FB?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=5efd2b233e121b975dbb594594d6d5a1&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B07BKQRWHT?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=a9e71c339701ed568e84051cdca36d0f&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B0CQ6Y4MJ8?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=9f78d77187cab4441df6da97c7935dfb&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B0841ZQMZ7?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=f30f7bb976bd3b50d27e141e06773cc7&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B07R3JF3Y3?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=fa31dc17e47301bd2ab39ada00a78a68&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B07PTPW6T9?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=aadd9f887364982f4f63a395630f2960&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B08CZBGHRK?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=8c893e18e23d746c74c7dbd63d59eca3&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B01N1RDG88?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=54c0d78cfe0cd47849235e4d35ac526e&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B0CC2HDFCP?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=25c1dd99ca9d7a1cd091e4373c998a00&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B08BNQJFMN?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=a96722aa36425f20e6a5caca1f9d7c8c&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B0F7383GQL?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=8125b6cedf4fd439149207881149bd61&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B077QC46H1?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=f7ae2b22ed411cea68677f99f0794f55&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B07K5M94LN?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=07ea1aa8445aef8fc1b2cb786b937f3e&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B00BTIVNT4?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=3a8ef12b71d246b8960ee47f841348af&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B08H9MR8K7?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=1b502a9c46988178640f07f6f1f9fb8e&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B07TP9S2JV?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=23a580153cd94ccaf3eac95ce37148ca&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B07TRT7HLL?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=c9925c5edddbf6fa657c6b0737fb0a8b&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B07TPB13T3?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=9b663beadbbb26b064d47aa417489896&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B0CPDKG7NW?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=f0e06233b6745b03492d52af49f5b6db&amp;ref_=as_li_ss_tl</t>
   </si>
 </sst>
 </file>
@@ -1366,7 +1285,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S91"/>
+  <dimension ref="A1:S82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1400,7 +1319,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>287</v>
+        <v>235</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -1456,7 +1375,7 @@
         <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>288</v>
+        <v>236</v>
       </c>
       <c r="E2" s="6">
         <v>0.1</v>
@@ -1497,7 +1416,7 @@
         <v>22</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>289</v>
+        <v>237</v>
       </c>
       <c r="E3" s="6">
         <v>0.1</v>
@@ -1536,7 +1455,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>290</v>
+        <v>238</v>
       </c>
       <c r="E4" s="6">
         <v>0.1</v>
@@ -1571,7 +1490,7 @@
         <v>26</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>291</v>
+        <v>239</v>
       </c>
       <c r="E5" s="6">
         <v>0.1</v>
@@ -1608,7 +1527,7 @@
         <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>292</v>
+        <v>240</v>
       </c>
       <c r="E6" s="6">
         <v>0.1</v>
@@ -1649,7 +1568,7 @@
         <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>293</v>
+        <v>241</v>
       </c>
       <c r="E7" s="6">
         <v>0.1</v>
@@ -1690,7 +1609,7 @@
         <v>33</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>294</v>
+        <v>242</v>
       </c>
       <c r="E8" s="6">
         <v>0.05</v>
@@ -1731,7 +1650,7 @@
         <v>35</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>295</v>
+        <v>243</v>
       </c>
       <c r="E9" s="6">
         <v>0.05</v>
@@ -1774,7 +1693,7 @@
         <v>37</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>296</v>
+        <v>244</v>
       </c>
       <c r="E10" s="6">
         <v>0.05</v>
@@ -1817,7 +1736,7 @@
         <v>40</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>297</v>
+        <v>245</v>
       </c>
       <c r="E11" s="6">
         <v>0.05</v>
@@ -1858,7 +1777,7 @@
         <v>43</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>298</v>
+        <v>246</v>
       </c>
       <c r="E12" s="6">
         <v>0.05</v>
@@ -1893,7 +1812,7 @@
         <v>46</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>299</v>
+        <v>247</v>
       </c>
       <c r="E13" s="6">
         <v>0.05</v>
@@ -1928,7 +1847,7 @@
         <v>48</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>300</v>
+        <v>248</v>
       </c>
       <c r="E14" s="6">
         <v>0.05</v>
@@ -1963,7 +1882,7 @@
         <v>51</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>301</v>
+        <v>249</v>
       </c>
       <c r="E15" s="6">
         <v>0.1</v>
@@ -1998,7 +1917,7 @@
         <v>53</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>302</v>
+        <v>250</v>
       </c>
       <c r="E16" s="6">
         <v>0.1</v>
@@ -2033,7 +1952,7 @@
         <v>56</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>303</v>
+        <v>251</v>
       </c>
       <c r="E17" s="6">
         <v>0.1</v>
@@ -2072,7 +1991,7 @@
         <v>59</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>304</v>
+        <v>252</v>
       </c>
       <c r="E18" s="6">
         <v>0.05</v>
@@ -2107,7 +2026,7 @@
         <v>63</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>305</v>
+        <v>253</v>
       </c>
       <c r="E19" s="6">
         <v>0.1</v>
@@ -2142,7 +2061,7 @@
         <v>65</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>306</v>
+        <v>254</v>
       </c>
       <c r="E20" s="6">
         <v>0.1</v>
@@ -2177,7 +2096,7 @@
         <v>68</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>307</v>
+        <v>255</v>
       </c>
       <c r="E21" s="6">
         <v>0.05</v>
@@ -2212,7 +2131,7 @@
         <v>70</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>308</v>
+        <v>256</v>
       </c>
       <c r="E22" s="6">
         <v>0.05</v>
@@ -2247,7 +2166,7 @@
         <v>72</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>309</v>
+        <v>257</v>
       </c>
       <c r="E23" s="6">
         <v>0.05</v>
@@ -2282,7 +2201,7 @@
         <v>75</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>310</v>
+        <v>258</v>
       </c>
       <c r="E24" s="6">
         <v>0.05</v>
@@ -2317,7 +2236,7 @@
         <v>77</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>311</v>
+        <v>259</v>
       </c>
       <c r="E25" s="6">
         <v>0.05</v>
@@ -2352,7 +2271,7 @@
         <v>80</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>312</v>
+        <v>260</v>
       </c>
       <c r="E26" s="6">
         <v>0.05</v>
@@ -2387,7 +2306,7 @@
         <v>82</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>313</v>
+        <v>261</v>
       </c>
       <c r="E27" s="6">
         <v>0.05</v>
@@ -2422,7 +2341,7 @@
         <v>84</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>314</v>
+        <v>262</v>
       </c>
       <c r="E28" s="6">
         <v>0.05</v>
@@ -2457,7 +2376,7 @@
         <v>86</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>315</v>
+        <v>263</v>
       </c>
       <c r="E29" s="6">
         <v>0.05</v>
@@ -2492,7 +2411,7 @@
         <v>88</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>316</v>
+        <v>264</v>
       </c>
       <c r="E30" s="6">
         <v>0.05</v>
@@ -2527,7 +2446,7 @@
         <v>90</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>317</v>
+        <v>265</v>
       </c>
       <c r="E31" s="6">
         <v>0.05</v>
@@ -2562,7 +2481,7 @@
         <v>93</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>318</v>
+        <v>266</v>
       </c>
       <c r="E32" s="6">
         <v>0.05</v>
@@ -2597,7 +2516,7 @@
         <v>95</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>319</v>
+        <v>267</v>
       </c>
       <c r="E33" s="6">
         <v>0.05</v>
@@ -2632,7 +2551,7 @@
         <v>97</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>320</v>
+        <v>268</v>
       </c>
       <c r="E34" s="6">
         <v>0.05</v>
@@ -2661,17 +2580,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>99</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="E35" s="6"/>
-      <c r="F35" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -2694,17 +2615,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E36" s="6"/>
-      <c r="F36" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -2727,17 +2650,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E37" s="6"/>
+        <v>271</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F37" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -2760,17 +2685,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E38" s="6"/>
+        <v>272</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F38" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
@@ -2793,17 +2720,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E39" s="6"/>
+        <v>273</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F39" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -2826,17 +2755,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E40" s="6"/>
+        <v>274</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F40" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
@@ -2859,17 +2790,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E41" s="6"/>
+        <v>275</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F41" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -2892,17 +2825,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E42" s="6"/>
+        <v>276</v>
+      </c>
+      <c r="E42" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F42" s="2" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
@@ -2925,17 +2860,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E43" s="6"/>
+        <v>277</v>
+      </c>
+      <c r="E43" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F43" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -2958,17 +2895,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>39</v>
+        <v>112</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E44" s="6"/>
+        <v>278</v>
+      </c>
+      <c r="E44" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F44" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -2991,17 +2930,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="E45" s="6"/>
+        <v>279</v>
+      </c>
+      <c r="E45" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F45" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -3024,17 +2965,19 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E46" s="6"/>
+        <v>280</v>
+      </c>
+      <c r="E46" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F46" s="2" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -3057,17 +3000,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E47" s="6"/>
+        <v>281</v>
+      </c>
+      <c r="E47" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F47" s="2" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -3090,17 +3035,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E48" s="6"/>
+        <v>282</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F48" s="2" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -3123,17 +3070,19 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E49" s="6"/>
+        <v>283</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F49" s="2" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -3156,17 +3105,19 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E50" s="6"/>
+        <v>284</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F50" s="2" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -3189,17 +3140,19 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E51" s="6"/>
+        <v>285</v>
+      </c>
+      <c r="E51" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F51" s="2" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -3222,17 +3175,19 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E52" s="6"/>
+        <v>286</v>
+      </c>
+      <c r="E52" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F52" s="2" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
@@ -3255,17 +3210,19 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>155</v>
+        <v>105</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E53" s="6"/>
+        <v>287</v>
+      </c>
+      <c r="E53" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F53" s="2" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -3288,17 +3245,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>155</v>
+        <v>55</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E54" s="6"/>
+        <v>288</v>
+      </c>
+      <c r="E54" s="6">
+        <v>0.1</v>
+      </c>
       <c r="F54" s="2" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -3321,17 +3280,19 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E55" s="6"/>
+        <v>289</v>
+      </c>
+      <c r="E55" s="6">
+        <v>0.1</v>
+      </c>
       <c r="F55" s="2" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
@@ -3354,17 +3315,19 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E56" s="6"/>
+        <v>290</v>
+      </c>
+      <c r="E56" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F56" s="2" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
@@ -3387,17 +3350,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>168</v>
+        <v>146</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E57" s="6"/>
+        <v>291</v>
+      </c>
+      <c r="E57" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F57" s="2" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -3420,17 +3385,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E58" s="6"/>
+        <v>292</v>
+      </c>
+      <c r="E58" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F58" s="2" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -3453,17 +3420,19 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E59" s="6"/>
+        <v>293</v>
+      </c>
+      <c r="E59" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F59" s="2" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
@@ -3486,17 +3455,17 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="E60" s="6"/>
       <c r="F60" s="2" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -3519,17 +3488,17 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="E61" s="6"/>
       <c r="F61" s="2" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
@@ -3552,17 +3521,17 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>55</v>
+        <v>155</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
       <c r="E62" s="6"/>
       <c r="F62" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
@@ -3585,17 +3554,17 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>55</v>
+        <v>155</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="E63" s="6"/>
       <c r="F63" s="2" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
@@ -3618,17 +3587,17 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>61</v>
+        <v>155</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="E64" s="6"/>
       <c r="F64" s="2" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
@@ -3651,17 +3620,17 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="E65" s="6"/>
       <c r="F65" s="2" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
@@ -3684,17 +3653,17 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
       <c r="E66" s="6"/>
       <c r="F66" s="2" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
@@ -3717,17 +3686,17 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="E67" s="6"/>
       <c r="F67" s="2" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -3750,17 +3719,17 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="E68" s="6"/>
       <c r="F68" s="2" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
@@ -3783,17 +3752,17 @@
         <v>68</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
       <c r="E69" s="6"/>
       <c r="F69" s="2" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -3816,17 +3785,17 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>207</v>
+        <v>105</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>208</v>
+        <v>183</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>209</v>
+        <v>184</v>
       </c>
       <c r="E70" s="6"/>
       <c r="F70" s="2" t="s">
-        <v>210</v>
+        <v>185</v>
       </c>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -3849,17 +3818,17 @@
         <v>70</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>207</v>
+        <v>105</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>211</v>
+        <v>186</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="E71" s="6"/>
       <c r="F71" s="2" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -3882,17 +3851,17 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>207</v>
+        <v>105</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>215</v>
+        <v>190</v>
       </c>
       <c r="E72" s="6"/>
       <c r="F72" s="2" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -3915,17 +3884,17 @@
         <v>72</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>207</v>
+        <v>105</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>217</v>
+        <v>192</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="E73" s="6"/>
       <c r="F73" s="2" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
@@ -3948,17 +3917,17 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>220</v>
+        <v>195</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="E74" s="6"/>
       <c r="F74" s="2" t="s">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
@@ -3981,17 +3950,17 @@
         <v>74</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="E75" s="6"/>
       <c r="F75" s="2" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
@@ -4014,17 +3983,17 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>226</v>
+        <v>201</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="E76" s="6"/>
       <c r="F76" s="2" t="s">
-        <v>228</v>
+        <v>203</v>
       </c>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -4050,14 +4019,14 @@
         <v>61</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
       <c r="E77" s="6"/>
       <c r="F77" s="2" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
@@ -4083,14 +4052,14 @@
         <v>61</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="E78" s="6"/>
       <c r="F78" s="2" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
@@ -4113,17 +4082,17 @@
         <v>78</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="E79" s="6"/>
       <c r="F79" s="2" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
@@ -4146,17 +4115,17 @@
         <v>79</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="E80" s="6"/>
       <c r="F80" s="2" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
@@ -4179,17 +4148,17 @@
         <v>80</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>129</v>
+        <v>61</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>242</v>
+        <v>217</v>
       </c>
       <c r="E81" s="6"/>
       <c r="F81" s="2" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
@@ -4212,17 +4181,17 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="E82" s="6"/>
       <c r="F82" s="2" t="s">
-        <v>246</v>
+        <v>221</v>
       </c>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
@@ -4239,303 +4208,6 @@
       <c r="Q82" s="2"/>
       <c r="R82" s="2"/>
       <c r="S82" s="2"/>
-    </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A83" s="2">
-        <v>82</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="E83" s="6"/>
-      <c r="F83" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K83" s="3"/>
-      <c r="L83" s="3"/>
-      <c r="M83" s="3"/>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" s="2"/>
-      <c r="Q83" s="2"/>
-      <c r="R83" s="2"/>
-      <c r="S83" s="2"/>
-    </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A84" s="2">
-        <v>83</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="E84" s="6"/>
-      <c r="F84" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K84" s="3"/>
-      <c r="L84" s="3"/>
-      <c r="M84" s="3"/>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
-      <c r="P84" s="2"/>
-      <c r="Q84" s="2"/>
-      <c r="R84" s="2"/>
-      <c r="S84" s="2"/>
-    </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A85" s="2">
-        <v>84</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E85" s="6"/>
-      <c r="F85" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K85" s="3"/>
-      <c r="L85" s="3"/>
-      <c r="M85" s="3"/>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
-      <c r="P85" s="2"/>
-      <c r="Q85" s="2"/>
-      <c r="R85" s="2"/>
-      <c r="S85" s="2"/>
-    </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A86" s="2">
-        <v>85</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E86" s="6"/>
-      <c r="F86" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K86" s="3"/>
-      <c r="L86" s="3"/>
-      <c r="M86" s="3"/>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
-      <c r="P86" s="2"/>
-      <c r="Q86" s="2"/>
-      <c r="R86" s="2"/>
-      <c r="S86" s="2"/>
-    </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A87" s="2">
-        <v>86</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E87" s="6"/>
-      <c r="F87" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K87" s="3"/>
-      <c r="L87" s="3"/>
-      <c r="M87" s="3"/>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" s="2"/>
-      <c r="Q87" s="2"/>
-      <c r="R87" s="2"/>
-      <c r="S87" s="2"/>
-    </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A88" s="2">
-        <v>87</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E88" s="6"/>
-      <c r="F88" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K88" s="3"/>
-      <c r="L88" s="3"/>
-      <c r="M88" s="3"/>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
-      <c r="P88" s="2"/>
-      <c r="Q88" s="2"/>
-      <c r="R88" s="2"/>
-      <c r="S88" s="2"/>
-    </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A89" s="2">
-        <v>88</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E89" s="6"/>
-      <c r="F89" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K89" s="3"/>
-      <c r="L89" s="3"/>
-      <c r="M89" s="3"/>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
-      <c r="P89" s="2"/>
-      <c r="Q89" s="2"/>
-      <c r="R89" s="2"/>
-      <c r="S89" s="2"/>
-    </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A90" s="2">
-        <v>89</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E90" s="6"/>
-      <c r="F90" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K90" s="3"/>
-      <c r="L90" s="3"/>
-      <c r="M90" s="3"/>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
-      <c r="P90" s="2"/>
-      <c r="Q90" s="2"/>
-      <c r="R90" s="2"/>
-      <c r="S90" s="2"/>
-    </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A91" s="2">
-        <v>90</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="E91" s="6"/>
-      <c r="F91" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K91" s="3"/>
-      <c r="L91" s="3"/>
-      <c r="M91" s="3"/>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
-      <c r="P91" s="2"/>
-      <c r="Q91" s="2"/>
-      <c r="R91" s="2"/>
-      <c r="S91" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4552,7 +4224,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>274</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -4560,17 +4232,17 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>275</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>276</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>277</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -4578,37 +4250,37 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>278</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>279</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>280</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>281</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>282</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>283</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>284</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -4616,12 +4288,12 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>285</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/products.xlsx
+++ b/products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kim_p\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9F6AE3-C4D6-4BEF-827A-6BF467D70205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694004CA-14B8-4A3A-BCEA-23B15060A8C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="247">
   <si>
     <t>id</t>
   </si>
@@ -206,9 +206,6 @@
     <t>Physio-trusted classic</t>
   </si>
   <si>
-    <t>Supplements</t>
-  </si>
-  <si>
     <t>Shakers</t>
   </si>
   <si>
@@ -482,213 +479,51 @@
     <t>Everfit Adjustable Foldable Weight Bench + Rack</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0B9WQJGKV?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Squat rack combo, folds flat</t>
   </si>
   <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>Blackmores Fish Oil 1000 Odourless (400 Caps)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B00UBMVS1M?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Australia's most trusted vitamin brand, ships from Amazon AU</t>
-  </si>
-  <si>
-    <t>Blackmores Fish Oil 1000 Odourless (200 Caps)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B074S69MSB?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Ranks #260 in ALL Amazon AU Health</t>
-  </si>
-  <si>
-    <t>Blackmores Omega Triple Super Strength Fish Oil</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B0773JF7JX?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>3x omega-3s, joint inflammation support</t>
-  </si>
-  <si>
-    <t>Pernaton Green Lipped Mussel Gel 1000ml</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B0013G6QNA?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Joint massage gel, original NZ mussel extract</t>
-  </si>
-  <si>
-    <t>ON Gold Standard 100% Whey 2.27kg (Double Rich Chocolate)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B07B33QR7C?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>#1 Best Seller in Whey, 4.4-star/5,916, 1K+ bought monthly</t>
-  </si>
-  <si>
-    <t>ON Gold Standard 100% Whey 4.54kg (Double Rich Chocolate)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B07B2W7FN9?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Bulk tub, best per-kg value</t>
-  </si>
-  <si>
-    <t>Muscle Nation Whey Protein Isolate 990g (Milk Chocolate)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B0DJ51QTTZ?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Aussie brand, 23.4g protein per serve</t>
-  </si>
-  <si>
-    <t>Muscle Nation RTD Protein Daily Shake 6x400ml</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B0F8TRB12C?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Ranks #633 in ALL Amazon AU Health</t>
-  </si>
-  <si>
-    <t>Muscle Nation Creatine Monohydrate 225g</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B0D47CJPPC?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Ships from Amazon AU, 75 serves</t>
-  </si>
-  <si>
     <t>Vulken Wooden Gymnastic Rings (1600lbs)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0832T4G82?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>"Best of TRX and rings" per AU reviews</t>
   </si>
   <si>
     <t>Vulken Adjustable Numbered Ring Straps</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B08BZ67DX5?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Upgrade/replacement straps, quick hook</t>
   </si>
   <si>
     <t>FINEX 8-in-1 Weight Bench (250kg)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0DRCXJK3R?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Foldable multi-station with bonus collars</t>
   </si>
   <si>
     <t>FINEX Olympic Multi-Station Weight Bench (330kg)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0F6LKYRVW?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Squat rack + lat pulldown + preacher</t>
   </si>
   <si>
     <t>LSG GRK200 10-in-1 Home Gym Station</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0CC4PYS6Y?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Smith machine + power rack + cables - biggest ticket in store</t>
   </si>
   <si>
     <t>Everfit 78kg Barbell Set (168cm Bar + Plates)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0B5KFZLKR?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Completes the bench/rack lineup - plates included</t>
   </si>
   <si>
     <t>Everfit 58kg Barbell Set (168cm Bar + Plates)</t>
   </si>
   <si>
-    <t>https://www.amazon.com.au/dp/B0B5G19FH7?tag=journeywith04-22</t>
-  </si>
-  <si>
     <t>Entry-size barbell set, rubber-coated plates</t>
   </si>
   <si>
-    <t>Musashi Bulk Extreme Protein 2kg (Chocolate)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B07QMYGY3Z?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>High-calorie mass gainer, sold by Amazon AU</t>
-  </si>
-  <si>
-    <t>Musashi High Protein 900g (Vanilla)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B07C5Q1Q8K?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Smaller starter tub, WPI-rich</t>
-  </si>
-  <si>
-    <t>ON Gold Standard 100% Whey 2.27kg (Vanilla Ice Cream)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B078RPW7Y3?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Ships from Amazon AU, tastes like melted ice cream per reviews</t>
-  </si>
-  <si>
-    <t>ON Gold Standard 100% Whey 907g (Vanilla Ice Cream)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B000GISTZ4?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Ranks #302 in ALL Amazon AU Health</t>
-  </si>
-  <si>
-    <t>Muscle Nation Whey Protein Isolate 990g (Strawberry Milkshake)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B0DJ536QBR?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>23.4g protein/serve, ships from Amazon AU</t>
-  </si>
-  <si>
-    <t>Muscle Nation Daily Greens 180g (Strawberry Pineapple)</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com.au/dp/B0F8V8S9CK?tag=journeywith04-22</t>
-  </si>
-  <si>
-    <t>Ranks #155 in ALL Amazon AU Health - superfood greens</t>
-  </si>
-  <si>
     <t>HOW TO USE — 100 verified Amazon AU products, IDs 1-100, all URLs pre-tagged. This IS the full catalogue.</t>
   </si>
   <si>
@@ -903,6 +738,30 @@
   </si>
   <si>
     <t>https://www.amazon.com.au/dp/B0CPDKG7NW?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=f0e06233b6745b03492d52af49f5b6db&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B07PM9B1YS?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=2447c1d63d38cb64e20d4aaebf53cab3&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B0832T4G82?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=12dc084dba02ab736e7ab593e460210b&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B08BZ67DX5?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=573938cfcd35804a3bf7a9d1b0e0b169&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B09D2JCR9R?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=1f4045d553879767690493696b6b6ddc&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B09YTWSTS4?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=872a1c52a70399dfd58bbb67b4b23854&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B0CC4PYS6Y?th=1&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=afbfeef852b11dd1c5ce6d4e47d86ac9&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B0B5KFZLKR?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=5e672f29c676bc0c23ea86d19375bd93&amp;ref_=as_li_ss_tl</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com.au/dp/B0B5G19FH7?&amp;linkCode=ll2&amp;tag=journeywith04-22&amp;linkId=e2791fe4978ceb65b70fc328f904f92b&amp;ref_=as_li_ss_tl</t>
   </si>
 </sst>
 </file>
@@ -1285,7 +1144,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S82"/>
+  <dimension ref="A1:S67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1319,7 +1178,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -1375,7 +1234,7 @@
         <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="E2" s="6">
         <v>0.1</v>
@@ -1416,7 +1275,7 @@
         <v>22</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>237</v>
+        <v>182</v>
       </c>
       <c r="E3" s="6">
         <v>0.1</v>
@@ -1455,7 +1314,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>238</v>
+        <v>183</v>
       </c>
       <c r="E4" s="6">
         <v>0.1</v>
@@ -1490,7 +1349,7 @@
         <v>26</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>239</v>
+        <v>184</v>
       </c>
       <c r="E5" s="6">
         <v>0.1</v>
@@ -1527,7 +1386,7 @@
         <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>240</v>
+        <v>185</v>
       </c>
       <c r="E6" s="6">
         <v>0.1</v>
@@ -1568,7 +1427,7 @@
         <v>30</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>241</v>
+        <v>186</v>
       </c>
       <c r="E7" s="6">
         <v>0.1</v>
@@ -1609,7 +1468,7 @@
         <v>33</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>242</v>
+        <v>187</v>
       </c>
       <c r="E8" s="6">
         <v>0.05</v>
@@ -1650,7 +1509,7 @@
         <v>35</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>243</v>
+        <v>188</v>
       </c>
       <c r="E9" s="6">
         <v>0.05</v>
@@ -1693,7 +1552,7 @@
         <v>37</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>244</v>
+        <v>189</v>
       </c>
       <c r="E10" s="6">
         <v>0.05</v>
@@ -1736,7 +1595,7 @@
         <v>40</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>245</v>
+        <v>190</v>
       </c>
       <c r="E11" s="6">
         <v>0.05</v>
@@ -1777,7 +1636,7 @@
         <v>43</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>246</v>
+        <v>191</v>
       </c>
       <c r="E12" s="6">
         <v>0.05</v>
@@ -1812,7 +1671,7 @@
         <v>46</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="E13" s="6">
         <v>0.05</v>
@@ -1847,7 +1706,7 @@
         <v>48</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>248</v>
+        <v>193</v>
       </c>
       <c r="E14" s="6">
         <v>0.05</v>
@@ -1882,7 +1741,7 @@
         <v>51</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>249</v>
+        <v>194</v>
       </c>
       <c r="E15" s="6">
         <v>0.1</v>
@@ -1917,7 +1776,7 @@
         <v>53</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="E16" s="6">
         <v>0.1</v>
@@ -1952,7 +1811,7 @@
         <v>56</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>251</v>
+        <v>196</v>
       </c>
       <c r="E17" s="6">
         <v>0.1</v>
@@ -1991,7 +1850,7 @@
         <v>59</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>252</v>
+        <v>197</v>
       </c>
       <c r="E18" s="6">
         <v>0.05</v>
@@ -2020,19 +1879,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>253</v>
+        <v>198</v>
       </c>
       <c r="E19" s="6">
         <v>0.1</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -2055,19 +1914,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>254</v>
+        <v>199</v>
       </c>
       <c r="E20" s="6">
         <v>0.1</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -2090,19 +1949,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -2128,16 +1987,16 @@
         <v>58</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
@@ -2163,16 +2022,16 @@
         <v>39</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
@@ -2195,19 +2054,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E24" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E24" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -2233,16 +2092,16 @@
         <v>50</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -2265,19 +2124,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
@@ -2300,19 +2159,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E27" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
@@ -2335,19 +2194,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
@@ -2370,19 +2229,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="E29" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
@@ -2405,19 +2264,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
@@ -2440,19 +2299,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E31" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
@@ -2475,19 +2334,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
@@ -2510,19 +2369,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E33" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
@@ -2545,19 +2404,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E34" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E34" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
@@ -2583,16 +2442,16 @@
         <v>39</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E35" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F35" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E35" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
@@ -2618,16 +2477,16 @@
         <v>39</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F36" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E36" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
@@ -2653,16 +2512,16 @@
         <v>39</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E37" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
@@ -2685,19 +2544,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E38" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="E38" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
@@ -2720,19 +2579,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F39" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="E39" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
@@ -2755,19 +2614,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F40" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="E40" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
@@ -2790,19 +2649,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E41" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
@@ -2825,19 +2684,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E42" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F42" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="E42" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
@@ -2860,19 +2719,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C43" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E43" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="E43" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
@@ -2895,19 +2754,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E44" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F44" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E44" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
@@ -2930,19 +2789,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E45" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="E45" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
@@ -2965,19 +2824,19 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="D46" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E46" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F46" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E46" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
@@ -3000,19 +2859,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C47" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E47" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F47" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E47" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
@@ -3035,19 +2894,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C48" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E48" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="E48" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
@@ -3070,19 +2929,19 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C49" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E49" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F49" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="E49" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
@@ -3105,19 +2964,19 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E50" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E50" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
@@ -3140,19 +2999,19 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C51" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E51" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="E51" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
@@ -3175,19 +3034,19 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E52" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E52" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
@@ -3210,19 +3069,19 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E53" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="E53" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -3248,16 +3107,16 @@
         <v>55</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>288</v>
+        <v>233</v>
       </c>
       <c r="E54" s="6">
         <v>0.1</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
@@ -3283,16 +3142,16 @@
         <v>55</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>289</v>
+        <v>234</v>
       </c>
       <c r="E55" s="6">
         <v>0.1</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
@@ -3315,19 +3174,19 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E56" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E56" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
@@ -3350,19 +3209,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E57" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F57" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="E57" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
@@ -3385,19 +3244,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E58" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F58" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E58" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
@@ -3420,19 +3279,19 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C59" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E59" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F59" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E59" s="6">
-        <v>0.05</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
@@ -3455,17 +3314,19 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E60" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="F60" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="E60" s="6"/>
-      <c r="F60" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
@@ -3488,17 +3349,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="E61" s="6"/>
+        <v>240</v>
+      </c>
+      <c r="E61" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F61" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
@@ -3521,17 +3384,19 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="D62" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E62" s="6"/>
+        <v>241</v>
+      </c>
+      <c r="E62" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F62" s="2" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
@@ -3554,17 +3419,19 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E63" s="6"/>
+        <v>242</v>
+      </c>
+      <c r="E63" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F63" s="2" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
@@ -3587,17 +3454,19 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>155</v>
+        <v>104</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E64" s="6"/>
+        <v>243</v>
+      </c>
+      <c r="E64" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F64" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
@@ -3620,17 +3489,19 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E65" s="6"/>
+        <v>244</v>
+      </c>
+      <c r="E65" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F65" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
@@ -3653,17 +3524,19 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E66" s="6"/>
+        <v>245</v>
+      </c>
+      <c r="E66" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F66" s="2" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
@@ -3686,17 +3559,19 @@
         <v>66</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E67" s="6"/>
+        <v>246</v>
+      </c>
+      <c r="E67" s="6">
+        <v>0.05</v>
+      </c>
       <c r="F67" s="2" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -3713,501 +3588,6 @@
       <c r="Q67" s="2"/>
       <c r="R67" s="2"/>
       <c r="S67" s="2"/>
-    </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A68" s="2">
-        <v>67</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E68" s="6"/>
-      <c r="F68" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K68" s="3"/>
-      <c r="L68" s="3"/>
-      <c r="M68" s="3"/>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
-      <c r="P68" s="2"/>
-      <c r="Q68" s="2"/>
-      <c r="R68" s="2"/>
-      <c r="S68" s="2"/>
-    </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A69" s="2">
-        <v>68</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="E69" s="6"/>
-      <c r="F69" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K69" s="3"/>
-      <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
-      <c r="P69" s="2"/>
-      <c r="Q69" s="2"/>
-      <c r="R69" s="2"/>
-      <c r="S69" s="2"/>
-    </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A70" s="2">
-        <v>69</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E70" s="6"/>
-      <c r="F70" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K70" s="3"/>
-      <c r="L70" s="3"/>
-      <c r="M70" s="3"/>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
-      <c r="P70" s="2"/>
-      <c r="Q70" s="2"/>
-      <c r="R70" s="2"/>
-      <c r="S70" s="2"/>
-    </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A71" s="2">
-        <v>70</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E71" s="6"/>
-      <c r="F71" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K71" s="3"/>
-      <c r="L71" s="3"/>
-      <c r="M71" s="3"/>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
-      <c r="P71" s="2"/>
-      <c r="Q71" s="2"/>
-      <c r="R71" s="2"/>
-      <c r="S71" s="2"/>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A72" s="2">
-        <v>71</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="E72" s="6"/>
-      <c r="F72" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K72" s="3"/>
-      <c r="L72" s="3"/>
-      <c r="M72" s="3"/>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
-      <c r="P72" s="2"/>
-      <c r="Q72" s="2"/>
-      <c r="R72" s="2"/>
-      <c r="S72" s="2"/>
-    </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A73" s="2">
-        <v>72</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E73" s="6"/>
-      <c r="F73" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3"/>
-      <c r="M73" s="3"/>
-      <c r="N73" s="2"/>
-      <c r="O73" s="2"/>
-      <c r="P73" s="2"/>
-      <c r="Q73" s="2"/>
-      <c r="R73" s="2"/>
-      <c r="S73" s="2"/>
-    </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A74" s="2">
-        <v>73</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E74" s="6"/>
-      <c r="F74" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K74" s="3"/>
-      <c r="L74" s="3"/>
-      <c r="M74" s="3"/>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" s="2"/>
-      <c r="Q74" s="2"/>
-      <c r="R74" s="2"/>
-      <c r="S74" s="2"/>
-    </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A75" s="2">
-        <v>74</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E75" s="6"/>
-      <c r="F75" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K75" s="3"/>
-      <c r="L75" s="3"/>
-      <c r="M75" s="3"/>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" s="2"/>
-      <c r="Q75" s="2"/>
-      <c r="R75" s="2"/>
-      <c r="S75" s="2"/>
-    </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A76" s="2">
-        <v>75</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E76" s="6"/>
-      <c r="F76" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K76" s="3"/>
-      <c r="L76" s="3"/>
-      <c r="M76" s="3"/>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" s="2"/>
-      <c r="Q76" s="2"/>
-      <c r="R76" s="2"/>
-      <c r="S76" s="2"/>
-    </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A77" s="2">
-        <v>76</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E77" s="6"/>
-      <c r="F77" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K77" s="3"/>
-      <c r="L77" s="3"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" s="2"/>
-      <c r="Q77" s="2"/>
-      <c r="R77" s="2"/>
-      <c r="S77" s="2"/>
-    </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A78" s="2">
-        <v>77</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E78" s="6"/>
-      <c r="F78" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K78" s="3"/>
-      <c r="L78" s="3"/>
-      <c r="M78" s="3"/>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" s="2"/>
-      <c r="Q78" s="2"/>
-      <c r="R78" s="2"/>
-      <c r="S78" s="2"/>
-    </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A79" s="2">
-        <v>78</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E79" s="6"/>
-      <c r="F79" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K79" s="3"/>
-      <c r="L79" s="3"/>
-      <c r="M79" s="3"/>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" s="2"/>
-      <c r="Q79" s="2"/>
-      <c r="R79" s="2"/>
-      <c r="S79" s="2"/>
-    </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
-        <v>79</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E80" s="6"/>
-      <c r="F80" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K80" s="3"/>
-      <c r="L80" s="3"/>
-      <c r="M80" s="3"/>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" s="2"/>
-      <c r="Q80" s="2"/>
-      <c r="R80" s="2"/>
-      <c r="S80" s="2"/>
-    </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A81" s="2">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E81" s="6"/>
-      <c r="F81" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K81" s="3"/>
-      <c r="L81" s="3"/>
-      <c r="M81" s="3"/>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" s="2"/>
-      <c r="Q81" s="2"/>
-      <c r="R81" s="2"/>
-      <c r="S81" s="2"/>
-    </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A82" s="2">
-        <v>81</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E82" s="6"/>
-      <c r="F82" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K82" s="3"/>
-      <c r="L82" s="3"/>
-      <c r="M82" s="3"/>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" s="2"/>
-      <c r="Q82" s="2"/>
-      <c r="R82" s="2"/>
-      <c r="S82" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4224,7 +3604,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>222</v>
+        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
@@ -4232,17 +3612,17 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>223</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>224</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>225</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -4250,37 +3630,37 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>226</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>227</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>228</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>229</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>230</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>231</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>232</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
@@ -4288,12 +3668,12 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>233</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>234</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
